--- a/Excel/Excercises/Mathematical.xlsx
+++ b/Excel/Excercises/Mathematical.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A958E0D1-DF8D-45B9-B48B-86DD90998665}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7246688-7262-4B27-A3F6-A3C7FE50C432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Exercise" sheetId="1" r:id="rId1"/>
